--- a/docs/pitch/applications/funding-pipeline.xlsx
+++ b/docs/pitch/applications/funding-pipeline.xlsx
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8034" uniqueCount="3352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8043" uniqueCount="3361">
   <si>
     <t>Score</t>
   </si>
@@ -10219,6 +10219,33 @@
   </si>
   <si>
     <t>Closing within 45d (apply-now)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submitted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUBMITTED 2026-08-16. Record: docs/pitch/applications/campus-founders/FILL-SHEET-38-FIELDS.md. 38 fields plus 2 conditional. Assets sent: Supaprod-Brief.pdf, founder video youtu.be/zBmtUtkTyBs, Supaprod-Product-Film.mp4. Login lantern@supaprod.ai, verified working 2026-08-16 11:25 IST. Pitch presentations 24-26 Aug, acceptances 28 Aug, move-in 30 Sep.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKIPPED by founder decision 2026-08-16. $100K for 8% is a $1.25M post, the worst price of any equity programme tracked; a16z Speedrun gives 5x the money for 2 more points. 10 weeks in person in Taipei collides with the Heilbronn onsite commitment filed the same day. Better India-accessible options already tracked: Peak XV Surge, Accel Atoms X, Emergent Ventures India. Was blocked on an intro video. Rolling, next batch Fall 2026, so re-openable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLOSED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT OPEN, verified 2026-08-16 20:30 IST. sequoiacap.com/arc/apply renders a blank page: nav, empty body, footer, no form, no closure notice, HTTP 200 so emptied not removed. The 2026-08-17 deadline this board carried was never verified against Sequoia's own page. Unresolved: outside sources say the open call is Americas and Europe only; Sequoia's own FAQ states no geography restriction.</t>
   </si>
 </sst>
 </file>
@@ -20266,11 +20293,15 @@
       <c r="R6" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="S6" s="5" t="s">
-        <v>3323</v>
-      </c>
-      <c r="T6" s="10"/>
-      <c r="U6" s="6"/>
+      <c r="S6" t="s">
+        <v>3352</v>
+      </c>
+      <c r="T6" t="s">
+        <v>3353</v>
+      </c>
+      <c r="U6" t="s">
+        <v>3354</v>
+      </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
@@ -20279,8 +20310,8 @@
       <c r="B7" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>19</v>
+      <c r="C7" t="s">
+        <v>3355</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>310</v>
@@ -20327,11 +20358,13 @@
       <c r="R7" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="S7" s="5" t="s">
-        <v>3323</v>
+      <c r="S7" t="s">
+        <v>3356</v>
       </c>
       <c r="T7" s="10"/>
-      <c r="U7" s="6"/>
+      <c r="U7" t="s">
+        <v>3357</v>
+      </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
@@ -41393,8 +41426,8 @@
       <c r="B377" s="5" t="s">
         <v>1787</v>
       </c>
-      <c r="C377" s="5" t="s">
-        <v>101</v>
+      <c r="C377" t="s">
+        <v>3358</v>
       </c>
       <c r="D377" s="6" t="s">
         <v>2222</v>
@@ -41405,8 +41438,8 @@
       <c r="F377" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G377" s="5" t="s">
-        <v>104</v>
+      <c r="G377" t="s">
+        <v>3359</v>
       </c>
       <c r="H377" s="5"/>
       <c r="I377" s="5"/>
@@ -41441,7 +41474,9 @@
         <v>3323</v>
       </c>
       <c r="T377" s="10"/>
-      <c r="U377" s="6"/>
+      <c r="U377" t="s">
+        <v>3360</v>
+      </c>
     </row>
     <row r="378" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A378" s="8">
